--- a/testdata/test_post_feed.xlsx
+++ b/testdata/test_post_feed.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -39,31 +39,75 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
       <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -78,44 +122,8 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -129,29 +137,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -161,7 +146,23 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -176,15 +177,7 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -204,55 +197,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -264,127 +359,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,6 +388,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -422,21 +454,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -446,26 +463,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -484,17 +488,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -503,10 +496,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -515,133 +508,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -661,7 +654,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1176,7 +1169,7 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>{'userID':11,'userKey':'dsaddasd','content':'test','imageIDList':'808401,808402','topicID':851}</t>
+          <t>{'userID':${userID},'userKey':${userKey},'content':'test','imageIDList':'808401,808402','topicID':851}</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -1191,12 +1184,12 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>{'result': False, 'errorCode': 0, 'errorMsg': 'User Key should contain at least 32 characters.'}</t>
+          <t>{'result': True, 'feed': {'id': 5656477, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645339265000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/testdata/test_post_feed.xlsx
+++ b/testdata/test_post_feed.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': 5656477, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645339265000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
+          <t>{'result': True, 'feed': {'id': 5656478, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645339856000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">

--- a/testdata/test_post_feed.xlsx
+++ b/testdata/test_post_feed.xlsx
@@ -40,50 +40,6 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
       <u val="single"/>
@@ -101,13 +57,6 @@
       <charset val="0"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -122,8 +71,90 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -137,14 +168,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
@@ -154,29 +177,6 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -197,187 +197,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -388,45 +388,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -458,18 +419,46 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -488,6 +477,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -496,10 +496,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -508,137 +508,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -654,7 +654,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -663,6 +666,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1077,8 +1081,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="15.6" outlineLevelRow="2"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="15.6" outlineLevelRow="4"/>
   <cols>
     <col width="12.7777777777778" customWidth="1" style="2" min="1" max="1"/>
     <col width="23.3333333333333" customWidth="1" style="1" min="2" max="2"/>
@@ -1088,7 +1092,9 @@
     <col width="25.6666666666667" customWidth="1" style="1" min="7" max="7"/>
     <col width="29.8888888888889" customWidth="1" style="1" min="8" max="8"/>
     <col width="18.3333333333333" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="10" customWidth="1" style="1" min="10" max="10"/>
+    <col width="17.6666666666667" customWidth="1" style="1" min="11" max="11"/>
+    <col width="10" customWidth="1" style="1" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
@@ -1142,6 +1148,11 @@
           <t>result</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>rely</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="24" customFormat="1" customHeight="1" s="1">
       <c r="A2" s="2" t="n">
@@ -1157,7 +1168,7 @@
           <t>post</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>http://47.111.114.205:12800/api-usr/learningFeed/postFeed</t>
         </is>
@@ -1184,12 +1195,17 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': 5656478, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645339856000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
+          <t>{'result': True, 'feed': {'id': 5656523, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645582599000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
           <t>PASS</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>['feedID',res.json()['feed']['id']]</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1223,7 @@
           <t>get</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>https://www.taobao.com</t>
         </is>
@@ -1217,12 +1233,12 @@
           <t>res.status_code==200</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>'www' in res.text</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;!DOCTYPE html&gt;
@@ -1266,10 +1282,111 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="24" customHeight="1" s="9">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>转发日记</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>http://47.111.114.205:12800/api-usr/learningCircle/forwardFeed</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'content':'这是一条转发','topicID':851,'relateID':${feedID},'type':10}</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True, 'feed': {'id': '5656524', 'author': {'id': '60556', 'gender': 'male', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'isOfficial': False, 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isMyself': True, 'isVerify': True}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645582600000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" s="9">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>点赞日记</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>http://47.111.114.205:12800/api-usr/learningFeed/likeFeed</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'feedID':${feedID}}</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True}</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" tooltip="http://47.111.114.205:12800/api-usr/learningFeed/postFeed" display="http://47.111.114.205:12800/api-usr/learningFeed/postFeed" r:id="rId1"/>
-    <hyperlink ref="D3" tooltip="https://www.taobao.com" display="https://www.taobao.com" r:id="rId2"/>
+    <hyperlink ref="D2" display="http://47.111.114.205:12800/api-usr/learningFeed/postFeed" r:id="rId1"/>
+    <hyperlink ref="D4" display="http://47.111.114.205:12800/api-usr/learningCircle/forwardFeed" r:id="rId2"/>
+    <hyperlink ref="D5" display="http://47.111.114.205:12800/api-usr/learningFeed/likeFeed" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/testdata/test_post_feed.xlsx
+++ b/testdata/test_post_feed.xlsx
@@ -48,7 +48,44 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -62,6 +99,66 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -71,99 +168,9 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -174,13 +181,6 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -197,187 +197,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -388,30 +388,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -439,11 +415,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -463,17 +460,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -496,10 +496,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -508,16 +508,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
@@ -526,119 +526,119 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -653,9 +653,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment vertical="center"/>
@@ -1081,8 +1078,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="15.6" outlineLevelRow="4"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="15.6"/>
   <cols>
     <col width="12.7777777777778" customWidth="1" style="2" min="1" max="1"/>
     <col width="23.3333333333333" customWidth="1" style="1" min="2" max="2"/>
@@ -1168,7 +1165,7 @@
           <t>post</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>http://47.111.114.205:12800/api-usr/learningFeed/postFeed</t>
         </is>
@@ -1195,7 +1192,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': 5656523, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645582599000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
+          <t>{'result': True, 'feed': {'id': 5656532, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645605553000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -1233,12 +1230,12 @@
           <t>res.status_code==200</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>'www' in res.text</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;!DOCTYPE html&gt;
@@ -1282,7 +1279,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" s="9">
+    <row r="4" ht="24" customHeight="1" s="8">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -1296,7 +1293,7 @@
           <t>post</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>http://47.111.114.205:12800/api-usr/learningCircle/forwardFeed</t>
         </is>
@@ -1323,7 +1320,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': '5656524', 'author': {'id': '60556', 'gender': 'male', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'isOfficial': False, 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isMyself': True, 'isVerify': True}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645582600000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
+          <t>{'result': True, 'feed': {'id': '5656533', 'author': {'id': '60556', 'gender': 'male', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'isOfficial': False, 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isMyself': True, 'isVerify': True}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645605555000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -1332,7 +1329,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="9">
+    <row r="5" ht="24" customHeight="1" s="8">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -1346,7 +1343,7 @@
           <t>post</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>http://47.111.114.205:12800/api-usr/learningFeed/likeFeed</t>
         </is>
@@ -1376,7 +1373,362 @@
           <t>{'result': True}</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" s="8">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>取消点赞日记</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>http://api.kr-cell.net/learning-feed/cancel-like-feed</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'feedID':${feedID}}</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True, 'errorCode': 0, 'errorMsg': '成功', 'data': None}</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" s="8">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>评论日记</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>http://47.111.114.205:12800/api-usr/learningCircle/postReply</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'feedID':${feedID},'content':'这是一条评论'}</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True, 'reply': {'id': '18860', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645605557000, 'author': {'id': '60556', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': True}, 'toUser': None}}</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>['replyID',res.json()['reply']['id']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" s="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>点赞评论</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>http://47.111.114.205:12800/api-usr/learningCircle/likeReply</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'replyID':${replyID}}</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True}</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" s="8">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>取消点赞评论</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>http://api.kr-cell.net/learning-feed/cancel-like-reply</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'replyID':${replyID}}</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True, 'errorCode': 0, 'errorMsg': '成功', 'data': None}</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="8">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>回复评论</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>http://47.111.114.205:12800/api-usr/learningCircle/postReply</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'replyID':${replyID},'content':'回复评论'}</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True, 'reply': {'id': '18861', 'replyID': '18860', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645605558000, 'author': {'id': '60556', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': True}, 'toUser': None}}</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" s="8">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>删除自己的一级评论</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>http://oldapi.kr-cell.net/learning-circle/delete-reply</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'replyID':${replyID}}</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True}</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" s="8">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>删除日记</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>http://47.111.114.205:12800/api-usr/learningCircle/deleteFeed</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>{'Content-Type':'application/json'}</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>{'userID':${userID},'userKey':${userKey},'feedID':${feedID}}</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>res.status_code==200</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>res.json()['result']==True</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>{'result': True}</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1387,6 +1739,13 @@
     <hyperlink ref="D2" display="http://47.111.114.205:12800/api-usr/learningFeed/postFeed" r:id="rId1"/>
     <hyperlink ref="D4" display="http://47.111.114.205:12800/api-usr/learningCircle/forwardFeed" r:id="rId2"/>
     <hyperlink ref="D5" display="http://47.111.114.205:12800/api-usr/learningFeed/likeFeed" r:id="rId3"/>
+    <hyperlink ref="D6" display="http://api.kr-cell.net/learning-feed/cancel-like-feed" r:id="rId4"/>
+    <hyperlink ref="D7" display="http://47.111.114.205:12800/api-usr/learningCircle/postReply" r:id="rId5"/>
+    <hyperlink ref="D8" display="http://47.111.114.205:12800/api-usr/learningCircle/likeReply" r:id="rId6"/>
+    <hyperlink ref="D9" display="http://api.kr-cell.net/learning-feed/cancel-like-reply" r:id="rId7"/>
+    <hyperlink ref="D10" display="http://47.111.114.205:12800/api-usr/learningCircle/postReply" r:id="rId8"/>
+    <hyperlink ref="D11" display="http://oldapi.kr-cell.net/learning-circle/delete-reply" r:id="rId9"/>
+    <hyperlink ref="D12" display="http://47.111.114.205:12800/api-usr/learningCircle/deleteFeed" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/testdata/test_post_feed.xlsx
+++ b/testdata/test_post_feed.xlsx
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': 5656532, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645605553000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
+          <t>{'result': True, 'feed': {'id': 5656553, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645705029000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': '5656533', 'author': {'id': '60556', 'gender': 'male', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'isOfficial': False, 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isMyself': True, 'isVerify': True}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645605555000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
+          <t>{'result': True, 'feed': {'id': '5656554', 'author': {'id': '60556', 'gender': 'male', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'isOfficial': False, 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isMyself': True, 'isVerify': True}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645705031000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'reply': {'id': '18860', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645605557000, 'author': {'id': '60556', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': True}, 'toUser': None}}</t>
+          <t>{'result': True, 'reply': {'id': '18868', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645705033000, 'author': {'id': '60556', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': True}, 'toUser': None}}</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'reply': {'id': '18861', 'replyID': '18860', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645605558000, 'author': {'id': '60556', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': True}, 'toUser': None}}</t>
+          <t>{'result': True, 'reply': {'id': '18869', 'replyID': '18868', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645705035000, 'author': {'id': '60556', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': True}, 'toUser': None}}</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">

--- a/testdata/test_post_feed.xlsx
+++ b/testdata/test_post_feed.xlsx
@@ -55,6 +55,50 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -70,22 +114,54 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -100,82 +176,6 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -197,187 +197,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -388,15 +388,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -430,17 +421,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -463,8 +448,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -472,8 +457,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -496,10 +496,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -508,133 +508,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': 5656553, 'author': {'id': 60556, 'nickname': '10000000185', 'avatarFile': '60556_1542805036963_9zibbh67eyqalp6od0m3', 'avatarID': '11259', 'gender': 'male', 'birthday': 974811355000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'categoryID': '108', 'categoryIDs': '108', 'regTime': '2018-11-21 20:55:54', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 11, 'followUserCount': 20, 'isVerify': True, 'authenticationInfo': {'type': 1, 'certList': []}, 'statusInfo': {'type': 1, 'startTime': 1619438026000, 'learningData': None}, 'accountType': 0, 'timingID': 575184202}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645705029000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
+          <t>{'result': True, 'feed': {'id': 5656606, 'author': {'id': 60646, 'nickname': '10000000184', 'avatarFile': '60646_1543897067000_bac64320h9rmg1i6i3pm', 'avatarID': '11900', 'gender': 'female', 'birthday': 844358400000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60646_1543897067000_bac64320h9rmg1i6i3pm', 'department': '假装自己是麻省理工大的学生', 'categoryAlias': 'BEC高级', 'categoryID': '9', 'categoryIDs': '9', 'regTime': '2018-12-04 12:14:09', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 14, 'followUserCount': 28, 'isVerify': False, 'authenticationInfo': None, 'statusInfo': {'type': 1, 'startTime': 1593774938000, 'learningData': None}, 'accountType': 0, 'timingID': 214144386}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645848242000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': '5656554', 'author': {'id': '60556', 'gender': 'male', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'isOfficial': False, 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isMyself': True, 'isVerify': True}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645705031000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
+          <t>{'result': True, 'feed': {'id': '5656607', 'author': {'id': '60646', 'gender': 'female', 'nickname': '10000000184', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60646_1543897067000_bac64320h9rmg1i6i3pm', 'isOfficial': False, 'department': '假装自己是麻省理工大的学生', 'categoryAlias': 'BEC高级', 'type': 'normal', 'isMyself': True, 'isVerify': False}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645848244000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'reply': {'id': '18868', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645705033000, 'author': {'id': '60556', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': True}, 'toUser': None}}</t>
+          <t>{'result': True, 'reply': {'id': '18888', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645848246000, 'author': {'id': '60646', 'nickname': '10000000184', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60646_1543897067000_bac64320h9rmg1i6i3pm', 'department': '假装自己是麻省理工大的学生', 'categoryAlias': 'BEC高级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'reply': {'id': '18869', 'replyID': '18868', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645705035000, 'author': {'id': '60556', 'nickname': '10000000185', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60556_1542805036963_9zibbh67eyqalp6od0m3', 'department': '要红包的', 'categoryAlias': '4级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': True}, 'toUser': None}}</t>
+          <t>{'result': True, 'reply': {'id': '18889', 'replyID': '18888', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645848248000, 'author': {'id': '60646', 'nickname': '10000000184', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60646_1543897067000_bac64320h9rmg1i6i3pm', 'department': '假装自己是麻省理工大的学生', 'categoryAlias': 'BEC高级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>res.json()['result']==True</t>
+          <t>res.json()['result']==False</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>

--- a/testdata/test_post_feed.xlsx
+++ b/testdata/test_post_feed.xlsx
@@ -62,7 +62,114 @@
     <font>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -74,113 +181,6 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -197,13 +197,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -215,13 +305,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,13 +323,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,25 +347,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,103 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,6 +402,65 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -429,65 +488,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -499,7 +499,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -508,10 +508,10 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -526,115 +526,115 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': 5656606, 'author': {'id': 60646, 'nickname': '10000000184', 'avatarFile': '60646_1543897067000_bac64320h9rmg1i6i3pm', 'avatarID': '11900', 'gender': 'female', 'birthday': 844358400000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60646_1543897067000_bac64320h9rmg1i6i3pm', 'department': '假装自己是麻省理工大的学生', 'categoryAlias': 'BEC高级', 'categoryID': '9', 'categoryIDs': '9', 'regTime': '2018-12-04 12:14:09', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 14, 'followUserCount': 28, 'isVerify': False, 'authenticationInfo': None, 'statusInfo': {'type': 1, 'startTime': 1593774938000, 'learningData': None}, 'accountType': 0, 'timingID': 214144386}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645848242000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
+          <t>{'result': True, 'feed': {'id': 5656670, 'author': {'id': 60554, 'nickname': '10000000182', 'avatarFile': 'timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'avatarID': '441116', 'gender': 'female', 'birthday': 978278400000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'categoryID': '24', 'categoryIDs': '24,7178', 'regTime': '2018-11-21 09:54:13', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 15, 'followUserCount': 34, 'isVerify': False, 'authenticationInfo': None, 'statusInfo': {'type': 1, 'startTime': 1630467342000, 'learningData': None}, 'accountType': 0, 'timingID': 243712457}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645867665000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>'www' in res.text</t>
+          <t>'都干啥的撒谎' in res.text</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': '5656607', 'author': {'id': '60646', 'gender': 'female', 'nickname': '10000000184', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60646_1543897067000_bac64320h9rmg1i6i3pm', 'isOfficial': False, 'department': '假装自己是麻省理工大的学生', 'categoryAlias': 'BEC高级', 'type': 'normal', 'isMyself': True, 'isVerify': False}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645848244000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
+          <t>{'result': True, 'feed': {'id': '5656671', 'author': {'id': '60554', 'gender': 'female', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'isOfficial': False, 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isMyself': True, 'isVerify': False}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645867666000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'reply': {'id': '18888', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645848246000, 'author': {'id': '60646', 'nickname': '10000000184', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60646_1543897067000_bac64320h9rmg1i6i3pm', 'department': '假装自己是麻省理工大的学生', 'categoryAlias': 'BEC高级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
+          <t>{'result': True, 'reply': {'id': '18949', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645867668000, 'author': {'id': '60554', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'reply': {'id': '18889', 'replyID': '18888', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645848248000, 'author': {'id': '60646', 'nickname': '10000000184', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/60646_1543897067000_bac64320h9rmg1i6i3pm', 'department': '假装自己是麻省理工大的学生', 'categoryAlias': 'BEC高级', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
+          <t>{'result': True, 'reply': {'id': '18950', 'replyID': '18949', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645867670000, 'author': {'id': '60554', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">

--- a/testdata/test_post_feed.xlsx
+++ b/testdata/test_post_feed.xlsx
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': 5656670, 'author': {'id': 60554, 'nickname': '10000000182', 'avatarFile': 'timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'avatarID': '441116', 'gender': 'female', 'birthday': 978278400000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'categoryID': '24', 'categoryIDs': '24,7178', 'regTime': '2018-11-21 09:54:13', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 15, 'followUserCount': 34, 'isVerify': False, 'authenticationInfo': None, 'statusInfo': {'type': 1, 'startTime': 1630467342000, 'learningData': None}, 'accountType': 0, 'timingID': 243712457}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1645867665000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
+          <t>{'result': True, 'feed': {'id': 5656794, 'author': {'id': 60554, 'nickname': '10000000182', 'avatarFile': 'timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'avatarID': '441116', 'gender': 'female', 'birthday': 978278400000, 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'categoryID': '24', 'categoryIDs': '24,7178', 'regTime': '2018-11-21 09:54:13', 'type': 'normal', 'isOfficial': False, 'disabled': False, 'fansCount': 15, 'followUserCount': 34, 'isVerify': False, 'authenticationInfo': None, 'statusInfo': {'type': 1, 'startTime': 1630467342000, 'learningData': None}, 'accountType': 0, 'timingID': 243712457}, 'content': 'test', 'type': 3, 'replyCount': None, 'likeCount': None, 'isLike': False, 'isAd': False, 'postTime': 1646124415000, 'tagList': [], 'imageList': [{'id': 808401, 'width': 1080, 'fileName': 'timing-test_60514_1922892798', 'height': 2340, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60514_1922892798?x-oss-process=image/resize,m_fill,w_300,h_300'}, {'id': 808402, 'width': 1080, 'fileName': 'light/freeLivetiming-test_60617_921901946', 'height': 1885, 'isGif': False, 'url': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946', 'shareImgUrl': 'http://timingtest-imgservice.kr-cell.com/image/light/freeLivetiming-test_60617_921901946?x-oss-process=image/resize,m_fill,w_300,h_300'}], 'learningRecord': None, 'video': None, 'web': None, 'replyList': [], 'topic': {'id': 851, 'name': '啊啊啊啊啊1213', 'type': 1}, 'svlogLabel': [], 'svlogClassification': None, 'originalType': 0, 'weather': {'city': '', 'name': '', 'postTime': ''}}}</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'feed': {'id': '5656671', 'author': {'id': '60554', 'gender': 'female', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'isOfficial': False, 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isMyself': True, 'isVerify': False}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1645867666000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
+          <t>{'result': True, 'feed': {'id': '5656795', 'author': {'id': '60554', 'gender': 'female', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'isOfficial': False, 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isMyself': True, 'isVerify': False}, 'source': 'timing', 'content': '您的版本过低，请升级到最新版查看完整内容~', 'type': 2, 'replyCount': '0', 'likeCount': '0', 'shareCount': '0', 'isLike': False, 'isAd': False, 'postTime': 1646124418000, 'imageList': [], 'learningRecord': None, 'video': None, 'topic': {'id': '851', 'name': '啊啊啊啊啊1213', 'user_count': '4', 'feed_count': '562', 'like_count': '118', 'reply_count': '190', 'is_official': '1', 'is_delete': '0', 'post_time': '2019-05-27 21:41:02', 'update_time': '2021-06-01 15:10:03', 'is_hot': '1', 'is_new': '0', 'user_id': '0', 'click_count': '554', 'feed_share_count': '7', 'feed_view_count': '39', 'isScreened': '0', 'super_topic': '0', 'channel_id': '0'}, 'web': None, 'replyList': None, 'groupData': None, 'feedData': None, 'album': None, 'payLive': None, 'freeLive': None, 'questionRoom': None, 'voiceChat': None, 'videoQuestionRoom': None}}</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'reply': {'id': '18949', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645867668000, 'author': {'id': '60554', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
+          <t>{'result': True, 'reply': {'id': '18967', 'replyID': '0', 'content': '这是一条评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1646124420000, 'author': {'id': '60554', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>{'result': True, 'reply': {'id': '18950', 'replyID': '18949', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1645867670000, 'author': {'id': '60554', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
+          <t>{'result': True, 'reply': {'id': '18968', 'replyID': '18967', 'content': '回复评论', 'likeCount': '0', 'replyCount': '0', 'postTime': 1646124423000, 'author': {'id': '60554', 'nickname': '10000000182', 'avatar': 'http://timingtest-imgservice.kr-cell.com/image/timing-test_60554_1561194874972_0l9uh2s4rie53enl2sod', 'department': '76', 'categoryAlias': '高考/艺考', 'type': 'normal', 'isOfficial': False, 'isMyself': True, 'isVerify': False}, 'toUser': None}}</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
